--- a/public/documents/pieces-reponse-1/R1-alcool-cuisine-controles.xlsx
+++ b/public/documents/pieces-reponse-1/R1-alcool-cuisine-controles.xlsx
@@ -3527,7 +3527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3940,16 +3940,16 @@
         </is>
       </c>
       <c r="B12" s="17" t="n">
-        <v>6.3</v>
+        <v>0.7</v>
       </c>
       <c r="C12" s="17" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="D12" s="17" t="n">
         <v>0.7</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>9.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="F12" s="17" t="n">
         <v>5.3</v>
@@ -3965,9 +3965,9 @@
       </c>
       <c r="J12" s="17" t="inlineStr"/>
       <c r="K12" s="17" t="inlineStr"/>
-      <c r="L12" s="20" t="inlineStr">
-        <is>
-          <t>non</t>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
     </row>
@@ -3981,13 +3981,13 @@
         <v>1.4</v>
       </c>
       <c r="C13" s="17" t="n">
-        <v>7.7</v>
+        <v>8.4</v>
       </c>
       <c r="D13" s="17" t="n">
         <v>7.7</v>
       </c>
       <c r="E13" s="17" t="n">
-        <v>16.8</v>
+        <v>17.5</v>
       </c>
       <c r="F13" s="17" t="n">
         <v>0</v>
@@ -4006,6 +4006,20 @@
       <c r="L13" s="20" t="inlineStr">
         <is>
           <t>non</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Liqueur de Poire : achats relus par code article 591050, 2 + 12 + 11 = 25 bouteilles de 70 cl, soit 17,5 L. La ligne du 15/03/2024 (facture n° 508974) porte une désignation tronquée, « LIQUEUR GOLDEN EIGHT 70 CL 25° », sans la mention « liqueur de poire William » : le rapprochement par libellé l’avait perdue. Le service en compte 25 lui aussi (annexe n° 6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Marc de Bourgogne : 4 bouteilles de 70 cl, 280 cl (code article 550252, Jacoulot 45°). Les 980 cl du cumul du dossier additionnaient deux produits distincts, ces 280 cl et 700 cl de marc du Jura Tissot 50° (code 520096, 10 bouteilles), qui est vendu au verre et n’entre pas dans ce tableau.</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4272,17 +4286,17 @@
         <v>5.58</v>
       </c>
       <c r="C12" s="17" t="n">
-        <v>5.58</v>
+        <v>2.1</v>
       </c>
       <c r="D12" s="17" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>5.58</v>
+        <v>2.1</v>
       </c>
       <c r="F12" s="22" t="inlineStr">
         <is>
-          <t>aucun retranchement identifié ; achats facturés 9,8 L contre 70 cl retenus par le service</t>
+          <t>aucun retranchement identifié ; 4 bouteilles facturées sur 3 exercices, 280 cl (code article 550252, Jacoulot 45°) contre 70 cl retenus par le service ; demande plafonnée à 210 cl, volume sorti du stock, et non aux 5,58 L calculés</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4320,7 @@
       </c>
       <c r="F13" s="22" t="inlineStr">
         <is>
-          <t>aucun retranchement identifié ; achats facturés 16,8 L contre 140 cl retenus par le service</t>
+          <t>aucun retranchement identifié ; 25 bouteilles facturées sur 3 exercices, 1 750 cl (code article 591050) contre 140 cl retenus par le service</t>
         </is>
       </c>
     </row>
@@ -4320,15 +4334,29 @@
         <v>794.62</v>
       </c>
       <c r="C14" s="19" t="n">
-        <v>744.61</v>
+        <v>741.13</v>
       </c>
       <c r="D14" s="19" t="n">
         <v>811.63</v>
       </c>
       <c r="E14" s="19" t="n">
-        <v>173.38</v>
+        <v>169.9</v>
       </c>
       <c r="F14" s="8" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Plafonnement : exercice par exercice pour tous les alcools, aux achats facturés. Le marc de bourgogne fait exception : il est plafonné sur les trois exercices pris ensemble aux 210 cl sortis du stock (280 cl facturés moins la bouteille inventoriée au 31/03/2025), parce que nous ne savons pas lequel des deux marcs achetés entre dans le baba.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>La colonne « demande initiale » n’est pas modifiée par ces plafonnements : elle reste le produit du nombre de plats par la dose, 119,1 L pour le Calvados en face de 73,0 L retenus, 5,58 L pour le marc de bourgogne en face de 2,10 L retenus.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
